--- a/rules/CORE-000890/negative/01/data/unit-test-coreid-FB1502-negative.xlsx
+++ b/rules/CORE-000890/negative/01/data/unit-test-coreid-FB1502-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000890\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8A1DA8-85A8-4DB1-9521-D940C8A32413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31CE11D-DD53-4337-ACDC-B352845A7BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,12 +584,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -646,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -659,17 +653,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -689,12 +676,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1094,22 +1079,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1146,7 +1131,7 @@
       <c r="D4" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>168</v>
       </c>
       <c r="F4" t="s">
@@ -1186,7 +1171,7 @@
       <c r="D6" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="13" t="s">
         <v>168</v>
       </c>
       <c r="F6" t="s">
@@ -1226,7 +1211,7 @@
       <c r="D8" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="13" t="s">
         <v>168</v>
       </c>
       <c r="F8" t="s">
@@ -1266,7 +1251,7 @@
       <c r="D10" t="s">
         <v>170</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="13" t="s">
         <v>168</v>
       </c>
       <c r="F10" t="s">
@@ -1306,7 +1291,7 @@
       <c r="D12" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="13" t="s">
         <v>168</v>
       </c>
       <c r="F12" t="s">
@@ -1351,7 +1336,7 @@
       <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -1575,7 +1560,7 @@
       <c r="B5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>58</v>
       </c>
       <c r="D5" s="5">
@@ -1608,10 +1593,10 @@
       <c r="N5" s="5">
         <v>151</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1637,7 +1622,7 @@
       <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="5" t="s">
         <v>62</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -1658,97 +1643,97 @@
       <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>1</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="7">
         <v>43</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="R7" s="8"/>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>4</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="7">
         <v>141</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <v>166</v>
       </c>
     </row>
@@ -1763,73 +1748,73 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="W1" s="10" t="s">
         <v>98</v>
       </c>
       <c r="X1" s="3" t="s">
@@ -1840,70 +1825,70 @@
       </c>
     </row>
     <row r="2" spans="1:25" ht="105" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="11" t="s">
         <v>117</v>
       </c>
       <c r="W2" s="4" t="s">
@@ -1917,70 +1902,70 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="A3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="14" t="s">
+      <c r="E3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="14" t="s">
+      <c r="Q3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="T3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="U3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="V3" s="14" t="s">
+      <c r="T3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>54</v>
       </c>
       <c r="W3" s="4" t="s">
@@ -1994,70 +1979,70 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="11">
         <v>12</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="11">
         <v>8</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>8</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>7</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>39</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <v>10</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="11">
         <v>6</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="11">
         <v>7</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="11">
         <v>200</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="11">
         <v>200</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="11">
         <v>8</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="11">
         <v>8</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="11">
         <v>7</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="11">
         <v>8</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="11">
         <v>8</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="11">
         <v>8</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="11">
         <v>1</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="11">
         <v>8</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="11">
         <v>200</v>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="11">
         <v>9</v>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="11">
         <v>19</v>
       </c>
       <c r="W4" s="4">
@@ -2131,7 +2116,7 @@
       <c r="V5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="X5" s="14" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2270,7 +2255,7 @@
       <c r="V7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="X7" s="14" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2421,66 +2406,66 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="9" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>162</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -2489,36 +2474,36 @@
       <c r="J2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="A3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="E3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>54</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -2527,36 +2512,36 @@
       <c r="J3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="11">
         <v>12</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="11">
         <v>8</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>8</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>7</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>26</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <v>9</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="11">
         <v>10</v>
       </c>
       <c r="I4" s="4">
@@ -2565,10 +2550,10 @@
       <c r="J4" s="4">
         <v>50</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="11">
         <v>8</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="11">
         <v>8</v>
       </c>
     </row>
@@ -2585,7 +2570,7 @@
       <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F5" s="5" t="s">
